--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/13.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/13.xlsx
@@ -426,13 +426,13 @@
         <v>-14.40606834805763</v>
       </c>
       <c r="E2">
-        <v>-12.04849365413577</v>
+        <v>-14.89656247334827</v>
       </c>
       <c r="F2">
-        <v>5.70570091771897</v>
+        <v>3.245338730172464</v>
       </c>
       <c r="G2">
-        <v>-16.99779384577662</v>
+        <v>-17.21357188623213</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.23568336631429</v>
       </c>
       <c r="E3">
-        <v>-12.49742672587046</v>
+        <v>-14.97571022156552</v>
       </c>
       <c r="F3">
-        <v>5.79481336944253</v>
+        <v>3.278450231997166</v>
       </c>
       <c r="G3">
-        <v>-15.96727421391091</v>
+        <v>-16.17123994046393</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.97541431813545</v>
       </c>
       <c r="E4">
-        <v>-12.14306642921344</v>
+        <v>-15.28859654993281</v>
       </c>
       <c r="F4">
-        <v>6.193062595482032</v>
+        <v>3.292933407667712</v>
       </c>
       <c r="G4">
-        <v>-16.16992281981771</v>
+        <v>-15.6536650467649</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.65986832694649</v>
       </c>
       <c r="E5">
-        <v>-11.98876216886209</v>
+        <v>-16.12764076140865</v>
       </c>
       <c r="F5">
-        <v>6.204103076226543</v>
+        <v>3.551796564307752</v>
       </c>
       <c r="G5">
-        <v>-15.69730364260536</v>
+        <v>-15.88163395908862</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.30554865246233</v>
       </c>
       <c r="E6">
-        <v>-13.32327203175599</v>
+        <v>-14.90256386371265</v>
       </c>
       <c r="F6">
-        <v>5.951843664521621</v>
+        <v>3.723266959952444</v>
       </c>
       <c r="G6">
-        <v>-15.17469784407926</v>
+        <v>-14.62651458079402</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.94493730768724</v>
       </c>
       <c r="E7">
-        <v>-13.05452603334899</v>
+        <v>-16.99273806752513</v>
       </c>
       <c r="F7">
-        <v>5.859430997065308</v>
+        <v>3.590999880012641</v>
       </c>
       <c r="G7">
-        <v>-15.15984401272812</v>
+        <v>-15.08345493136444</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.5983509170477</v>
       </c>
       <c r="E8">
-        <v>-14.60824654317867</v>
+        <v>-17.24919886683329</v>
       </c>
       <c r="F8">
-        <v>6.256677898547423</v>
+        <v>3.960226425727659</v>
       </c>
       <c r="G8">
-        <v>-13.01980100692501</v>
+        <v>-14.68934998161293</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.2799702604782</v>
       </c>
       <c r="E9">
-        <v>-14.51206232210697</v>
+        <v>-18.04181432890887</v>
       </c>
       <c r="F9">
-        <v>6.148428503084388</v>
+        <v>4.096183054079531</v>
       </c>
       <c r="G9">
-        <v>-13.2047109087075</v>
+        <v>-14.17190693051576</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.00365529272266</v>
       </c>
       <c r="E10">
-        <v>-14.46986984825803</v>
+        <v>-18.31488797351635</v>
       </c>
       <c r="F10">
-        <v>6.762127806918014</v>
+        <v>4.614050189818087</v>
       </c>
       <c r="G10">
-        <v>-13.04660291089738</v>
+        <v>-13.52767698446805</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.76991079493414</v>
       </c>
       <c r="E11">
-        <v>-15.23325916224079</v>
+        <v>-19.23197102578571</v>
       </c>
       <c r="F11">
-        <v>6.178132101413974</v>
+        <v>5.005657566021942</v>
       </c>
       <c r="G11">
-        <v>-12.25081532521866</v>
+        <v>-13.8343415710017</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.58644490407616</v>
       </c>
       <c r="E12">
-        <v>-16.45061524008393</v>
+        <v>-19.57799167410248</v>
       </c>
       <c r="F12">
-        <v>7.02174146442499</v>
+        <v>4.662382114301827</v>
       </c>
       <c r="G12">
-        <v>-11.33680539222056</v>
+        <v>-12.86031714671538</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.44234689396612</v>
       </c>
       <c r="E13">
-        <v>-16.66580142524595</v>
+        <v>-20.21733702544658</v>
       </c>
       <c r="F13">
-        <v>6.904393281409607</v>
+        <v>5.349229573272259</v>
       </c>
       <c r="G13">
-        <v>-11.56787064762934</v>
+        <v>-12.50774653266389</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.33797535771929</v>
       </c>
       <c r="E14">
-        <v>-18.11107743417304</v>
+        <v>-20.33233114060844</v>
       </c>
       <c r="F14">
-        <v>7.510647219026869</v>
+        <v>5.644375222154918</v>
       </c>
       <c r="G14">
-        <v>-10.2695460570964</v>
+        <v>-12.68998955884656</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.2559972858503</v>
       </c>
       <c r="E15">
-        <v>-19.46254901211754</v>
+        <v>-21.31927951378407</v>
       </c>
       <c r="F15">
-        <v>8.032449099928723</v>
+        <v>5.499033191129327</v>
       </c>
       <c r="G15">
-        <v>-11.49541465299217</v>
+        <v>-12.03780467402973</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.17888539921426</v>
       </c>
       <c r="E16">
-        <v>-20.31303947400461</v>
+        <v>-21.78933581831684</v>
       </c>
       <c r="F16">
-        <v>8.210360880497584</v>
+        <v>5.802265362598114</v>
       </c>
       <c r="G16">
-        <v>-9.513939136047215</v>
+        <v>-11.29883863900429</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.08808736287842</v>
       </c>
       <c r="E17">
-        <v>-19.88243867705771</v>
+        <v>-22.48239049851362</v>
       </c>
       <c r="F17">
-        <v>7.78150347892464</v>
+        <v>5.877421480319308</v>
       </c>
       <c r="G17">
-        <v>-9.881052902843496</v>
+        <v>-11.28618566534347</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.96077288718956</v>
       </c>
       <c r="E18">
-        <v>-20.59131293919077</v>
+        <v>-23.06799329531445</v>
       </c>
       <c r="F18">
-        <v>8.889827585909073</v>
+        <v>6.170956782970924</v>
       </c>
       <c r="G18">
-        <v>-9.317249554669628</v>
+        <v>-11.27500123551514</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.78431684887719</v>
       </c>
       <c r="E19">
-        <v>-21.42833868996274</v>
+        <v>-24.10743825963591</v>
       </c>
       <c r="F19">
-        <v>8.559913700396114</v>
+        <v>6.43457973870745</v>
       </c>
       <c r="G19">
-        <v>-8.92884124961593</v>
+        <v>-10.6756108278198</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.54226995438833</v>
       </c>
       <c r="E20">
-        <v>-21.98304990092949</v>
+        <v>-24.44651473861756</v>
       </c>
       <c r="F20">
-        <v>8.843142455822099</v>
+        <v>6.121387277587401</v>
       </c>
       <c r="G20">
-        <v>-8.364684145549965</v>
+        <v>-10.40975478998985</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.23928404209723</v>
       </c>
       <c r="E21">
-        <v>-21.76802569100914</v>
+        <v>-25.90193288959988</v>
       </c>
       <c r="F21">
-        <v>9.362035110405319</v>
+        <v>6.605412291451986</v>
       </c>
       <c r="G21">
-        <v>-7.99003315911914</v>
+        <v>-9.669821474093407</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.876989957858678</v>
       </c>
       <c r="E22">
-        <v>-22.92992809124317</v>
+        <v>-25.38098313349266</v>
       </c>
       <c r="F22">
-        <v>9.219280899146074</v>
+        <v>6.3697931241345</v>
       </c>
       <c r="G22">
-        <v>-8.201739743384811</v>
+        <v>-9.010400910642309</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.472830593355082</v>
       </c>
       <c r="E23">
-        <v>-23.70852231188613</v>
+        <v>-26.46806543170991</v>
       </c>
       <c r="F23">
-        <v>8.744793707557324</v>
+        <v>6.255367421316194</v>
       </c>
       <c r="G23">
-        <v>-8.797150070950995</v>
+        <v>-8.797370678868942</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.043227903784851</v>
       </c>
       <c r="E24">
-        <v>-22.59877178625797</v>
+        <v>-25.92888307788669</v>
       </c>
       <c r="F24">
-        <v>9.355509232006066</v>
+        <v>6.410666428523434</v>
       </c>
       <c r="G24">
-        <v>-6.739134049456076</v>
+        <v>-8.565759777840624</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.605305912055897</v>
       </c>
       <c r="E25">
-        <v>-25.18321551662698</v>
+        <v>-27.803459928616</v>
       </c>
       <c r="F25">
-        <v>8.93953460028146</v>
+        <v>6.619786122625364</v>
       </c>
       <c r="G25">
-        <v>-7.764928233611874</v>
+        <v>-8.605631069236106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.178803023450687</v>
       </c>
       <c r="E26">
-        <v>-23.48765038042042</v>
+        <v>-26.53164279067038</v>
       </c>
       <c r="F26">
-        <v>9.604009512437083</v>
+        <v>6.520975145349827</v>
       </c>
       <c r="G26">
-        <v>-7.482225060935468</v>
+        <v>-8.356452467854185</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.77480795009432</v>
       </c>
       <c r="E27">
-        <v>-23.38299360824607</v>
+        <v>-27.05559531856545</v>
       </c>
       <c r="F27">
-        <v>8.752441195419969</v>
+        <v>6.249013843336722</v>
       </c>
       <c r="G27">
-        <v>-6.914406387580466</v>
+        <v>-8.095744818357907</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.411063210070341</v>
       </c>
       <c r="E28">
-        <v>-24.34096502600837</v>
+        <v>-28.56241776611517</v>
       </c>
       <c r="F28">
-        <v>8.592259790740629</v>
+        <v>5.981479336724177</v>
       </c>
       <c r="G28">
-        <v>-6.064034659363046</v>
+        <v>-7.444758265308401</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.091340605856264</v>
       </c>
       <c r="E29">
-        <v>-23.15748253973053</v>
+        <v>-27.72869381834644</v>
       </c>
       <c r="F29">
-        <v>8.383976747715527</v>
+        <v>6.074476831566866</v>
       </c>
       <c r="G29">
-        <v>-6.413216526935266</v>
+        <v>-7.198789574401253</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.827531260380137</v>
       </c>
       <c r="E30">
-        <v>-23.79608861945881</v>
+        <v>-27.80945716576905</v>
       </c>
       <c r="F30">
-        <v>8.874216173835913</v>
+        <v>5.858065847585495</v>
       </c>
       <c r="G30">
-        <v>-6.453098261309113</v>
+        <v>-7.005800723481569</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.621842469397365</v>
       </c>
       <c r="E31">
-        <v>-24.15153290427162</v>
+        <v>-28.5140556968432</v>
       </c>
       <c r="F31">
-        <v>8.581905198205634</v>
+        <v>6.129344574858694</v>
       </c>
       <c r="G31">
-        <v>-6.184243783316266</v>
+        <v>-6.526755198458192</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.474585939194055</v>
       </c>
       <c r="E32">
-        <v>-23.81479883647717</v>
+        <v>-27.91676783997998</v>
       </c>
       <c r="F32">
-        <v>8.95431764495182</v>
+        <v>5.787353092612918</v>
       </c>
       <c r="G32">
-        <v>-6.927554097341313</v>
+        <v>-6.81468116568912</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.387944225914395</v>
       </c>
       <c r="E33">
-        <v>-24.12413416916172</v>
+        <v>-27.89660399899793</v>
       </c>
       <c r="F33">
-        <v>8.540905981971475</v>
+        <v>5.882961601509231</v>
       </c>
       <c r="G33">
-        <v>-5.299441555431245</v>
+        <v>-6.522674604662281</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.355711244117016</v>
       </c>
       <c r="E34">
-        <v>-22.73295373774053</v>
+        <v>-28.3899868149366</v>
       </c>
       <c r="F34">
-        <v>8.519669955233308</v>
+        <v>5.846866320299646</v>
       </c>
       <c r="G34">
-        <v>-6.069023792276663</v>
+        <v>-6.100044659508272</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.37709714062791</v>
       </c>
       <c r="E35">
-        <v>-22.96822069965809</v>
+        <v>-27.21769515657351</v>
       </c>
       <c r="F35">
-        <v>8.653906892856968</v>
+        <v>5.912956785164601</v>
       </c>
       <c r="G35">
-        <v>-5.860268654771246</v>
+        <v>-5.952067656083971</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.442081200103353</v>
       </c>
       <c r="E36">
-        <v>-24.9586181546029</v>
+        <v>-27.4505075705981</v>
       </c>
       <c r="F36">
-        <v>8.562877598963331</v>
+        <v>6.207525890334911</v>
       </c>
       <c r="G36">
-        <v>-5.928852915179792</v>
+        <v>-5.903040483407454</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.547580628813363</v>
       </c>
       <c r="E37">
-        <v>-21.95365762438368</v>
+        <v>-26.54042267941107</v>
       </c>
       <c r="F37">
-        <v>8.566063499994497</v>
+        <v>6.174780526902246</v>
       </c>
       <c r="G37">
-        <v>-5.94334254766047</v>
+        <v>-5.537609341500145</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.685982372510891</v>
       </c>
       <c r="E38">
-        <v>-22.66591675374647</v>
+        <v>-27.44500041238138</v>
       </c>
       <c r="F38">
-        <v>8.844804160832114</v>
+        <v>6.339544460053874</v>
       </c>
       <c r="G38">
-        <v>-6.904112221657706</v>
+        <v>-6.096598476648002</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.848306401773671</v>
       </c>
       <c r="E39">
-        <v>-22.31239540577707</v>
+        <v>-26.4943427997621</v>
       </c>
       <c r="F39">
-        <v>8.870712179722071</v>
+        <v>6.545531268638416</v>
       </c>
       <c r="G39">
-        <v>-5.806051321847596</v>
+        <v>-5.315641225619103</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.030941427831421</v>
       </c>
       <c r="E40">
-        <v>-21.5826097246235</v>
+        <v>-26.56248869117988</v>
       </c>
       <c r="F40">
-        <v>9.277954162286365</v>
+        <v>6.674643925508358</v>
       </c>
       <c r="G40">
-        <v>-5.882298117631059</v>
+        <v>-5.824480567916265</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.22319990187078</v>
       </c>
       <c r="E41">
-        <v>-22.80067184839186</v>
+        <v>-25.25892440586728</v>
       </c>
       <c r="F41">
-        <v>9.151243770884541</v>
+        <v>6.777797204709369</v>
       </c>
       <c r="G41">
-        <v>-6.772593352135783</v>
+        <v>-6.074229616991344</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.422080270328478</v>
       </c>
       <c r="E42">
-        <v>-20.31579720632429</v>
+        <v>-25.81823737498193</v>
       </c>
       <c r="F42">
-        <v>8.571492619952444</v>
+        <v>6.645926084388105</v>
       </c>
       <c r="G42">
-        <v>-6.773491448275126</v>
+        <v>-6.206711851267388</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.618914825980367</v>
       </c>
       <c r="E43">
-        <v>-21.72511886481234</v>
+        <v>-25.12026113936522</v>
       </c>
       <c r="F43">
-        <v>8.439069806940916</v>
+        <v>6.879235763386585</v>
       </c>
       <c r="G43">
-        <v>-7.086480563580743</v>
+        <v>-6.660049374302072</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.81027360577669</v>
       </c>
       <c r="E44">
-        <v>-20.52612413423626</v>
+        <v>-25.25142370621463</v>
       </c>
       <c r="F44">
-        <v>9.286663617159398</v>
+        <v>6.915975514435549</v>
       </c>
       <c r="G44">
-        <v>-6.932496236852289</v>
+        <v>-6.639910090526223</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.990732800408842</v>
       </c>
       <c r="E45">
-        <v>-20.28102652111283</v>
+        <v>-24.26793911128391</v>
       </c>
       <c r="F45">
-        <v>9.349001577689672</v>
+        <v>6.996852337440476</v>
       </c>
       <c r="G45">
-        <v>-6.377514594651791</v>
+        <v>-6.51099152261705</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.155029961741509</v>
       </c>
       <c r="E46">
-        <v>-20.91943739990885</v>
+        <v>-23.53700714380469</v>
       </c>
       <c r="F46">
-        <v>8.415991491098922</v>
+        <v>7.340639720215521</v>
       </c>
       <c r="G46">
-        <v>-7.132706407310994</v>
+        <v>-7.455911366201637</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.303267390481542</v>
       </c>
       <c r="E47">
-        <v>-17.72431793597103</v>
+        <v>-23.35631337869537</v>
       </c>
       <c r="F47">
-        <v>9.17822038372411</v>
+        <v>7.214853786835222</v>
       </c>
       <c r="G47">
-        <v>-6.259796121038494</v>
+        <v>-7.76904537783206</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.429715364260915</v>
       </c>
       <c r="E48">
-        <v>-19.15693495678003</v>
+        <v>-23.43960187860348</v>
       </c>
       <c r="F48">
-        <v>8.956416727950513</v>
+        <v>6.904310444669327</v>
       </c>
       <c r="G48">
-        <v>-7.806693620208209</v>
+        <v>-7.954660180654145</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.538675219143713</v>
       </c>
       <c r="E49">
-        <v>-18.38166330519694</v>
+        <v>-23.9406286799855</v>
       </c>
       <c r="F49">
-        <v>8.917678954725998</v>
+        <v>7.090166268631035</v>
       </c>
       <c r="G49">
-        <v>-7.680307474552415</v>
+        <v>-7.366516860657327</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.627543116266938</v>
       </c>
       <c r="E50">
-        <v>-17.98447509335829</v>
+        <v>-23.12352173072741</v>
       </c>
       <c r="F50">
-        <v>9.061627671780078</v>
+        <v>7.165998334152913</v>
       </c>
       <c r="G50">
-        <v>-7.031205879097692</v>
+        <v>-7.564006635252091</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.700478419085281</v>
       </c>
       <c r="E51">
-        <v>-17.64399898216017</v>
+        <v>-23.32153438706126</v>
       </c>
       <c r="F51">
-        <v>9.241356890430682</v>
+        <v>6.988707829136152</v>
       </c>
       <c r="G51">
-        <v>-7.805781164973615</v>
+        <v>-7.75341615533736</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.75665385844057</v>
       </c>
       <c r="E52">
-        <v>-17.03209389803921</v>
+        <v>-21.88055695185537</v>
       </c>
       <c r="F52">
-        <v>9.149176165847154</v>
+        <v>7.086261344694238</v>
       </c>
       <c r="G52">
-        <v>-8.360768028663294</v>
+        <v>-8.443522105340108</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.799869309489589</v>
       </c>
       <c r="E53">
-        <v>-18.67623397162173</v>
+        <v>-21.86059246501692</v>
       </c>
       <c r="F53">
-        <v>8.577942288550641</v>
+        <v>6.974368789393692</v>
       </c>
       <c r="G53">
-        <v>-7.47728292142449</v>
+        <v>-8.275888805889315</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.83437707385284</v>
       </c>
       <c r="E54">
-        <v>-16.13976398526582</v>
+        <v>-21.7393643796565</v>
       </c>
       <c r="F54">
-        <v>8.736796648650698</v>
+        <v>7.218909473639329</v>
       </c>
       <c r="G54">
-        <v>-8.025077183765653</v>
+        <v>-8.408042086346878</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.859687877359951</v>
       </c>
       <c r="E55">
-        <v>-16.25589192711935</v>
+        <v>-21.61401215545052</v>
       </c>
       <c r="F55">
-        <v>8.458458574370841</v>
+        <v>6.948430949277234</v>
       </c>
       <c r="G55">
-        <v>-8.557830946517413</v>
+        <v>-8.596874631877512</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.885024254782465</v>
       </c>
       <c r="E56">
-        <v>-16.87373195022349</v>
+        <v>-19.8819361384874</v>
       </c>
       <c r="F56">
-        <v>8.553951111830763</v>
+        <v>7.153831273740593</v>
       </c>
       <c r="G56">
-        <v>-9.18891057205968</v>
+        <v>-8.689660494645677</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.911111608381912</v>
       </c>
       <c r="E57">
-        <v>-17.09438791470031</v>
+        <v>-20.55034150947133</v>
       </c>
       <c r="F57">
-        <v>8.301975001777597</v>
+        <v>7.088724909350163</v>
       </c>
       <c r="G57">
-        <v>-9.232613131142621</v>
+        <v>-8.354639305735656</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.946513513233624</v>
       </c>
       <c r="E58">
-        <v>-15.86572264241966</v>
+        <v>-20.66960097266379</v>
       </c>
       <c r="F58">
-        <v>8.687430921648264</v>
+        <v>7.261094911994296</v>
       </c>
       <c r="G58">
-        <v>-9.120563889408926</v>
+        <v>-9.072654115417405</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.991592176566025</v>
       </c>
       <c r="E59">
-        <v>-15.85405627180821</v>
+        <v>-20.56710802358967</v>
       </c>
       <c r="F59">
-        <v>8.282178677585495</v>
+        <v>6.857004039030253</v>
       </c>
       <c r="G59">
-        <v>-8.540713599605779</v>
+        <v>-8.568681201038078</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.051696620548221</v>
       </c>
       <c r="E60">
-        <v>-14.66546118238951</v>
+        <v>-20.43833355325204</v>
       </c>
       <c r="F60">
-        <v>8.835016171600635</v>
+        <v>7.158259725875959</v>
       </c>
       <c r="G60">
-        <v>-9.367871892291314</v>
+        <v>-9.380195912133663</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.127502606869902</v>
       </c>
       <c r="E61">
-        <v>-15.347426788349</v>
+        <v>-19.76113583389344</v>
       </c>
       <c r="F61">
-        <v>8.583250466867781</v>
+        <v>7.471811698448823</v>
       </c>
       <c r="G61">
-        <v>-9.079324567847699</v>
+        <v>-9.444792260179284</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.217110539106706</v>
       </c>
       <c r="E62">
-        <v>-14.95164236193814</v>
+        <v>-19.32123599679025</v>
       </c>
       <c r="F62">
-        <v>8.4460777951686</v>
+        <v>7.095413147760366</v>
       </c>
       <c r="G62">
-        <v>-9.272148941858145</v>
+        <v>-9.784672044773368</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.322980322067068</v>
       </c>
       <c r="E63">
-        <v>-14.14214824903846</v>
+        <v>-19.68679750439033</v>
       </c>
       <c r="F63">
-        <v>8.334244882321055</v>
+        <v>7.104180588351597</v>
       </c>
       <c r="G63">
-        <v>-9.225301740915208</v>
+        <v>-9.363940110937097</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.438332287003162</v>
       </c>
       <c r="E64">
-        <v>-14.74009438989668</v>
+        <v>-19.66385101182066</v>
       </c>
       <c r="F64">
-        <v>8.635175849144865</v>
+        <v>6.914005656751692</v>
       </c>
       <c r="G64">
-        <v>-9.942496776795348</v>
+        <v>-9.551699640440782</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.564478481941165</v>
       </c>
       <c r="E65">
-        <v>-13.99578492874018</v>
+        <v>-19.26187414732448</v>
       </c>
       <c r="F65">
-        <v>8.666746587600359</v>
+        <v>6.829359762064027</v>
       </c>
       <c r="G65">
-        <v>-9.85220548048399</v>
+        <v>-9.347126915770328</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.693845467955173</v>
       </c>
       <c r="E66">
-        <v>-14.55592438690848</v>
+        <v>-20.43257720235582</v>
       </c>
       <c r="F66">
-        <v>8.412558736581721</v>
+        <v>7.420578831320479</v>
       </c>
       <c r="G66">
-        <v>-9.322270016518338</v>
+        <v>-10.1458659482093</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.825681190151498</v>
       </c>
       <c r="E67">
-        <v>-14.22674916372522</v>
+        <v>-20.18924055083412</v>
       </c>
       <c r="F67">
-        <v>8.532251199347026</v>
+        <v>6.782122939286788</v>
       </c>
       <c r="G67">
-        <v>-8.946696131874553</v>
+        <v>-9.146384153415037</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.95343506810012</v>
       </c>
       <c r="E68">
-        <v>-13.97274291231003</v>
+        <v>-19.36067904474215</v>
       </c>
       <c r="F68">
-        <v>7.815609021632702</v>
+        <v>6.918149150500495</v>
       </c>
       <c r="G68">
-        <v>-9.577848858265373</v>
+        <v>-9.629789621905571</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.07403791421574</v>
       </c>
       <c r="E69">
-        <v>-13.60456903478663</v>
+        <v>-19.46416045811158</v>
       </c>
       <c r="F69">
-        <v>8.125347190683076</v>
+        <v>7.195745007587443</v>
       </c>
       <c r="G69">
-        <v>-9.486318763645533</v>
+        <v>-9.695545140549648</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.18629676573058</v>
       </c>
       <c r="E70">
-        <v>-13.95862614701694</v>
+        <v>-18.55925046823528</v>
       </c>
       <c r="F70">
-        <v>8.651905557211805</v>
+        <v>6.951484311523953</v>
       </c>
       <c r="G70">
-        <v>-8.991504341291831</v>
+        <v>-9.723796007770083</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.28255115600464</v>
       </c>
       <c r="E71">
-        <v>-14.29836713981056</v>
+        <v>-18.61543926424889</v>
       </c>
       <c r="F71">
-        <v>8.323426404040493</v>
+        <v>7.059765184948293</v>
       </c>
       <c r="G71">
-        <v>-9.065195218120595</v>
+        <v>-9.709003528916837</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.36490408188223</v>
       </c>
       <c r="E72">
-        <v>-15.56899230610596</v>
+        <v>-19.19980855728624</v>
       </c>
       <c r="F72">
-        <v>8.50905691206864</v>
+        <v>6.745083319238011</v>
       </c>
       <c r="G72">
-        <v>-8.838491211551274</v>
+        <v>-10.20203481271481</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.42652877184714</v>
       </c>
       <c r="E73">
-        <v>-16.44733420313732</v>
+        <v>-19.53332388630395</v>
       </c>
       <c r="F73">
-        <v>7.785864004932977</v>
+        <v>7.027028105189657</v>
       </c>
       <c r="G73">
-        <v>-9.145397291959595</v>
+        <v>-9.89808801130051</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.46917633761694</v>
       </c>
       <c r="E74">
-        <v>-15.28704324889732</v>
+        <v>-18.50663758717236</v>
       </c>
       <c r="F74">
-        <v>8.223689312008627</v>
+        <v>7.009682091775034</v>
       </c>
       <c r="G74">
-        <v>-9.462233339420218</v>
+        <v>-10.03838681488235</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.48672004013476</v>
       </c>
       <c r="E75">
-        <v>-14.77622317521136</v>
+        <v>-18.43312159351157</v>
       </c>
       <c r="F75">
-        <v>7.852360369825305</v>
+        <v>6.834276950967045</v>
       </c>
       <c r="G75">
-        <v>-8.064222688164806</v>
+        <v>-10.22366613702448</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.48182099143988</v>
       </c>
       <c r="E76">
-        <v>-17.1023662336553</v>
+        <v>-19.5974826948499</v>
       </c>
       <c r="F76">
-        <v>7.897948741470973</v>
+        <v>7.035396272692737</v>
       </c>
       <c r="G76">
-        <v>-9.527041157777717</v>
+        <v>-10.09208983112155</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.45289703408806</v>
       </c>
       <c r="E77">
-        <v>-15.60261670499177</v>
+        <v>-20.70213307697117</v>
       </c>
       <c r="F77">
-        <v>7.956612064202428</v>
+        <v>7.302352578858128</v>
       </c>
       <c r="G77">
-        <v>-9.009103370580526</v>
+        <v>-9.732258736362178</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.39841040373426</v>
       </c>
       <c r="E78">
-        <v>-16.04988849219653</v>
+        <v>-20.43264780694835</v>
       </c>
       <c r="F78">
-        <v>7.746503299421556</v>
+        <v>6.815204619884989</v>
       </c>
       <c r="G78">
-        <v>-8.73258113572358</v>
+        <v>-9.097960062739066</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.3212785993811</v>
       </c>
       <c r="E79">
-        <v>-15.51558200846866</v>
+        <v>-19.95375762192766</v>
       </c>
       <c r="F79">
-        <v>7.415222607693978</v>
+        <v>6.907189849761457</v>
       </c>
       <c r="G79">
-        <v>-7.94470280078364</v>
+        <v>-9.36916551623621</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.21793595876333</v>
       </c>
       <c r="E80">
-        <v>-17.28313060335714</v>
+        <v>-20.14926173862132</v>
       </c>
       <c r="F80">
-        <v>8.207642178681596</v>
+        <v>6.848447003759333</v>
       </c>
       <c r="G80">
-        <v>-8.364919112563165</v>
+        <v>-8.965810698398389</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.09145585237943</v>
       </c>
       <c r="E81">
-        <v>-17.39691198081215</v>
+        <v>-20.87861963900843</v>
       </c>
       <c r="F81">
-        <v>8.445145053473048</v>
+        <v>6.815960090956342</v>
       </c>
       <c r="G81">
-        <v>-8.028695675768937</v>
+        <v>-9.08851699955301</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.936592440318288</v>
       </c>
       <c r="E82">
-        <v>-18.86380960789629</v>
+        <v>-21.71018391688825</v>
       </c>
       <c r="F82">
-        <v>7.959549455012755</v>
+        <v>6.63565432859339</v>
       </c>
       <c r="G82">
-        <v>-7.777727408969807</v>
+        <v>-8.686829142136615</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.757492603504504</v>
       </c>
       <c r="E83">
-        <v>-18.99761777035961</v>
+        <v>-22.89739183372447</v>
       </c>
       <c r="F83">
-        <v>7.611037064572141</v>
+        <v>7.169036785786381</v>
       </c>
       <c r="G83">
-        <v>-7.034231732078792</v>
+        <v>-8.38909591284917</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.549488699808238</v>
       </c>
       <c r="E84">
-        <v>-20.48395242644395</v>
+        <v>-23.39882149660499</v>
       </c>
       <c r="F84">
-        <v>7.888336366128887</v>
+        <v>6.491145635175017</v>
       </c>
       <c r="G84">
-        <v>-7.4146459371945</v>
+        <v>-7.869222258537667</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.316076882941498</v>
       </c>
       <c r="E85">
-        <v>-19.54199994476151</v>
+        <v>-24.70320396454859</v>
       </c>
       <c r="F85">
-        <v>7.902783093633711</v>
+        <v>6.765885281457113</v>
       </c>
       <c r="G85">
-        <v>-7.647246310422852</v>
+        <v>-8.306639461055743</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.058115500903146</v>
       </c>
       <c r="E86">
-        <v>-23.22321956857991</v>
+        <v>-25.6998334733224</v>
       </c>
       <c r="F86">
-        <v>7.759472219479785</v>
+        <v>7.267088978520953</v>
       </c>
       <c r="G86">
-        <v>-7.089976350588243</v>
+        <v>-7.433586889203027</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.777457044147834</v>
       </c>
       <c r="E87">
-        <v>-24.33455246772284</v>
+        <v>-26.25158344461455</v>
       </c>
       <c r="F87">
-        <v>8.02391194547547</v>
+        <v>6.566725877006444</v>
       </c>
       <c r="G87">
-        <v>-6.78302066603269</v>
+        <v>-7.4249870965199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.479521822218903</v>
       </c>
       <c r="E88">
-        <v>-24.38248467962268</v>
+        <v>-27.22576069296633</v>
       </c>
       <c r="F88">
-        <v>8.557368955734713</v>
+        <v>7.463110527249817</v>
       </c>
       <c r="G88">
-        <v>-6.571790542654896</v>
+        <v>-7.180436039925727</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.164873758739635</v>
       </c>
       <c r="E89">
-        <v>-25.62303228950367</v>
+        <v>-28.11367574210142</v>
       </c>
       <c r="F89">
-        <v>8.025152839844864</v>
+        <v>6.958379641784855</v>
       </c>
       <c r="G89">
-        <v>-5.55490291367168</v>
+        <v>-6.897238131149305</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.842674306874294</v>
       </c>
       <c r="E90">
-        <v>-30.63222877480202</v>
+        <v>-28.87006689500184</v>
       </c>
       <c r="F90">
-        <v>7.739316383834868</v>
+        <v>7.321784421392999</v>
       </c>
       <c r="G90">
-        <v>-5.491905646688116</v>
+        <v>-6.618287903822623</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.511244519822596</v>
       </c>
       <c r="E91">
-        <v>-28.71146821414062</v>
+        <v>-30.48944967587707</v>
       </c>
       <c r="F91">
-        <v>7.89906041052553</v>
+        <v>6.876280148493397</v>
       </c>
       <c r="G91">
-        <v>-5.625270312635957</v>
+        <v>-5.903233678507197</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.180769670282632</v>
       </c>
       <c r="E92">
-        <v>-31.25949658761353</v>
+        <v>-32.30759892094159</v>
       </c>
       <c r="F92">
-        <v>7.604145047780849</v>
+        <v>6.781369124950241</v>
       </c>
       <c r="G92">
-        <v>-5.58454530775918</v>
+        <v>-6.187982369570741</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.851665359378367</v>
       </c>
       <c r="E93">
-        <v>-32.24504532857269</v>
+        <v>-33.5553938845844</v>
       </c>
       <c r="F93">
-        <v>7.883921167871966</v>
+        <v>6.8992723141255</v>
       </c>
       <c r="G93">
-        <v>-5.160194881919627</v>
+        <v>-6.340008637855858</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.527949498870579</v>
       </c>
       <c r="E94">
-        <v>-34.50325015616509</v>
+        <v>-35.48018098362523</v>
       </c>
       <c r="F94">
-        <v>7.14150019658252</v>
+        <v>6.853496731446799</v>
       </c>
       <c r="G94">
-        <v>-5.337910876981299</v>
+        <v>-6.027121341589296</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.212951148290606</v>
       </c>
       <c r="E95">
-        <v>-35.25064960654726</v>
+        <v>-37.77225940278294</v>
       </c>
       <c r="F95">
-        <v>7.827187941189033</v>
+        <v>6.754382571701838</v>
       </c>
       <c r="G95">
-        <v>-4.413286961848027</v>
+        <v>-5.81699034168436</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.909004350592663</v>
       </c>
       <c r="E96">
-        <v>-39.70400105418718</v>
+        <v>-39.13031797388862</v>
       </c>
       <c r="F96">
-        <v>7.002032947177584</v>
+        <v>6.804672756725796</v>
       </c>
       <c r="G96">
-        <v>-4.25973862946629</v>
+        <v>-5.153983920537368</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.623255558460714</v>
       </c>
       <c r="E97">
-        <v>-41.27573611813831</v>
+        <v>-42.02921379329437</v>
       </c>
       <c r="F97">
-        <v>6.616008767268598</v>
+        <v>6.40545434082502</v>
       </c>
       <c r="G97">
-        <v>-4.645209846854985</v>
+        <v>-5.713482150880492</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.359092996272806</v>
       </c>
       <c r="E98">
-        <v>-42.70215031783368</v>
+        <v>-43.70874130397009</v>
       </c>
       <c r="F98">
-        <v>6.63689687969759</v>
+        <v>6.437421038899052</v>
       </c>
       <c r="G98">
-        <v>-4.914745729186111</v>
+        <v>-5.493383328126686</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.126715326227334</v>
       </c>
       <c r="E99">
-        <v>-47.03644373303042</v>
+        <v>-45.44123887188268</v>
       </c>
       <c r="F99">
-        <v>6.803160157848285</v>
+        <v>6.371305723012012</v>
       </c>
       <c r="G99">
-        <v>-5.068928472503488</v>
+        <v>-5.578172480212273</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.934945971999324</v>
       </c>
       <c r="E100">
-        <v>-47.22104359339073</v>
+        <v>-47.74128418866424</v>
       </c>
       <c r="F100">
-        <v>6.549318564404015</v>
+        <v>5.929628507513344</v>
       </c>
       <c r="G100">
-        <v>-3.996740051591311</v>
+        <v>-4.562336981299276</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.788323823374198</v>
       </c>
       <c r="E101">
-        <v>-50.6004015883036</v>
+        <v>-49.34082811734358</v>
       </c>
       <c r="F101">
-        <v>5.444501765003036</v>
+        <v>6.120878660002083</v>
       </c>
       <c r="G101">
-        <v>-5.006448132948965</v>
+        <v>-4.878641742235605</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.705903059789299</v>
       </c>
       <c r="E102">
-        <v>-51.54448466739568</v>
+        <v>-51.41164524147387</v>
       </c>
       <c r="F102">
-        <v>5.242863885283191</v>
+        <v>6.081885749617505</v>
       </c>
       <c r="G102">
-        <v>-5.161581187297508</v>
+        <v>-4.803086793768787</v>
       </c>
     </row>
   </sheetData>
